--- a/Data/Home/LivingRoom.Noise.xlsx
+++ b/Data/Home/LivingRoom.Noise.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:I205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709278316</v>
+        <v>1711874836</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709278351</v>
+        <v>1711874871</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709281555</v>
+        <v>1711879375</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -561,10 +568,15 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709281603</v>
+        <v>1711887951</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +605,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709283571</v>
+        <v>1711887986</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +642,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709283620</v>
+        <v>1711887997</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +671,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709287531</v>
+        <v>1711973571</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709287557</v>
+        <v>1711973616</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +737,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +760,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709269239</v>
+        <v>1711973639</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +770,15 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709269290</v>
+        <v>1711980685</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +811,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709272559</v>
+        <v>1711980719</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +844,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709272610</v>
+        <v>1712042400</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +873,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709352603</v>
+        <v>1712042437</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +906,15 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +933,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709352641</v>
+        <v>1712046928</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +947,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +966,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709352664</v>
+        <v>1712046956</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +976,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +999,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709357085</v>
+        <v>1712046973</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1009,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1032,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709357134</v>
+        <v>1712050992</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1046,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1065,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709359053</v>
+        <v>1712051022</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1075,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1098,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709444736</v>
+        <v>1712055537</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1112,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1131,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709444797</v>
+        <v>1712055572</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1141,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1164,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709444847</v>
+        <v>1712057054</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1174,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1197,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709450376</v>
+        <v>1712057098</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1211,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709450416</v>
+        <v>1712064320</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1244,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709450440</v>
+        <v>1712064342</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1277,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709452409</v>
+        <v>1712133990</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1310,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1329,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709452457</v>
+        <v>1712134030</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1343,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1362,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709456664</v>
+        <v>1712139086</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1376,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709456716</v>
+        <v>1712139121</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1409,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1428,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709538130</v>
+        <v>1712147297</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1442,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1461,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709538171</v>
+        <v>1712147333</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1494,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709549316</v>
+        <v>1712147345</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1504,15 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1531,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709549361</v>
+        <v>1712157087</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1541,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1564,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709612804</v>
+        <v>1712157107</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1578,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1597,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709612856</v>
+        <v>1712225355</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1630,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709616894</v>
+        <v>1712225403</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1644,11 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1667,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709619390</v>
+        <v>1712233570</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1681,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1700,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709619423</v>
+        <v>1712233600</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1714,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1733,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709619441</v>
+        <v>1712302884</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1743,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1766,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709626050</v>
+        <v>1712302914</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1776,15 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1803,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709626100</v>
+        <v>1712307940</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1817,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1836,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709626130</v>
+        <v>1712307974</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1846,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1869,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709631087</v>
+        <v>1712311590</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1902,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709631115</v>
+        <v>1712311619</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1912,15 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1939,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709631145</v>
+        <v>1712316497</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1949,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1972,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709770242</v>
+        <v>1712316529</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1986,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2005,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709770276</v>
+        <v>1712316539</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2015,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2038,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709776294</v>
+        <v>1712364660</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2052,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2071,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709776330</v>
+        <v>1712364693</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2081,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2104,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709788852</v>
+        <v>1712369251</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2118,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2137,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709788900</v>
+        <v>1712369285</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2147,11 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2170,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709788928</v>
+        <v>1712456500</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2180,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2203,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709795070</v>
+        <v>1712456538</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2217,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2236,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709795102</v>
+        <v>1712456550</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2161,10 +2246,15 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2273,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709795123</v>
+        <v>1712462144</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2283,11 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2306,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709875604</v>
+        <v>1712462176</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2320,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2339,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709875654</v>
+        <v>1712478956</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2353,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2372,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709879765</v>
+        <v>1712478987</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2382,15 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2409,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709879807</v>
+        <v>1712484522</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2419,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2442,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709973493</v>
+        <v>1712484547</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2456,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2475,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709973541</v>
+        <v>1712573793</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2489,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2508,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709978252</v>
+        <v>1712573823</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2518,15 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2545,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709978287</v>
+        <v>1712579249</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2555,11 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2578,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710032381</v>
+        <v>1712579282</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2592,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2611,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710032416</v>
+        <v>1712649747</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2625,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2644,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710037077</v>
+        <v>1712649782</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2654,15 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2681,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710037114</v>
+        <v>1712654953</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2691,11 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2714,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710059221</v>
+        <v>1712654985</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2728,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2747,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710059268</v>
+        <v>1712656695</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2761,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2780,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710063703</v>
+        <v>1712656737</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2790,15 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2817,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710063747</v>
+        <v>1712662074</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2827,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2850,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710139341</v>
+        <v>1712662097</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2864,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2883,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710139376</v>
+        <v>1712742875</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2897,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2916,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710141282</v>
+        <v>1712742901</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2930,11 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2953,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710147593</v>
+        <v>1712747598</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2967,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2986,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710147637</v>
+        <v>1712747626</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3000,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3019,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710148090</v>
+        <v>1712747640</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3033,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3052,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710227758</v>
+        <v>1712817987</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3066,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3085,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710227805</v>
+        <v>1712818021</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3099,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3118,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710227835</v>
+        <v>1712823189</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3128,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3151,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710238817</v>
+        <v>1712823214</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3161,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3184,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710238857</v>
+        <v>1712830533</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3198,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3217,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710238885</v>
+        <v>1712830569</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3227,11 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3250,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710288843</v>
+        <v>1712835383</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3264,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3283,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710288885</v>
+        <v>1712835417</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3293,11 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3316,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710296720</v>
+        <v>1712918142</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3330,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3349,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710296745</v>
+        <v>1712918173</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3359,11 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3382,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710492892</v>
+        <v>1712926356</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3396,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3415,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710492933</v>
+        <v>1712926391</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3425,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3448,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710498488</v>
+        <v>1712975668</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3462,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3481,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710498528</v>
+        <v>1712975711</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3491,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3514,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710567392</v>
+        <v>1712980562</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3528,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3547,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710567436</v>
+        <v>1712980598</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3557,11 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3580,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710569554</v>
+        <v>1713056623</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3590,11 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3613,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710573834</v>
+        <v>1713056652</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3627,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3646,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710573871</v>
+        <v>1713056664</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3505,10 +3656,15 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3683,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710573901</v>
+        <v>1713066802</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3693,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3716,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710650966</v>
+        <v>1713066839</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3730,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3749,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710651003</v>
+        <v>1713151439</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3763,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3782,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710658037</v>
+        <v>1713151471</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3633,10 +3792,15 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3819,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710658089</v>
+        <v>1713156685</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3829,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3852,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710663243</v>
+        <v>1713156714</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3866,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3885,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710663294</v>
+        <v>1713182852</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3899,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3918,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710670541</v>
+        <v>1713182885</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3928,15 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3955,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710670579</v>
+        <v>1713190655</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3965,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3988,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710743779</v>
+        <v>1713190691</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4002,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4021,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710743827</v>
+        <v>1713248660</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4035,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4054,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710747843</v>
+        <v>1713248688</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4064,15 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4091,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710747895</v>
+        <v>1713258217</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4101,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4124,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710836835</v>
+        <v>1713258243</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4138,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4157,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710836895</v>
+        <v>1713258260</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4167,11 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4190,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710841496</v>
+        <v>1713276235</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4204,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4223,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710841536</v>
+        <v>1713276271</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4233,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4256,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710916134</v>
+        <v>1713283554</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4270,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4289,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710916174</v>
+        <v>1713283586</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4299,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4322,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710920730</v>
+        <v>1713337565</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4336,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4355,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710920782</v>
+        <v>1713337601</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4365,11 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4388,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710978420</v>
+        <v>1713337617</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4398,15 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4425,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710978471</v>
+        <v>1713346931</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4439,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4458,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710978501</v>
+        <v>1713346961</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4273,10 +4468,11 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4491,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710982663</v>
+        <v>1713350824</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4505,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4524,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710982701</v>
+        <v>1713350865</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4534,15 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4561,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710982736</v>
+        <v>1713351482</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4571,11 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4594,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711084052</v>
+        <v>1713351507</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4608,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4627,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711084107</v>
+        <v>1713355580</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4433,10 +4637,11 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4660,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711084131</v>
+        <v>1713432635</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4670,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4693,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711089174</v>
+        <v>1713432669</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4707,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4726,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711089203</v>
+        <v>1713437408</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4740,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4759,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711089632</v>
+        <v>1713437442</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4769,11 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4792,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711089684</v>
+        <v>1713445346</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4802,11 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4825,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711092328</v>
+        <v>1713445377</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4839,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4858,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711092365</v>
+        <v>1713451043</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4872,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4891,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711095362</v>
+        <v>1713451075</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4905,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4924,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711165886</v>
+        <v>1713531292</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4938,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4957,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711165935</v>
+        <v>1713531329</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4971,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4990,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711169525</v>
+        <v>1713536374</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +5004,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5023,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711169559</v>
+        <v>1713536410</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5037,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5056,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711180413</v>
+        <v>1713574886</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5070,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5089,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711180451</v>
+        <v>1713574917</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5103,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5122,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711180474</v>
+        <v>1713574931</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5136,11 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5159,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711186624</v>
+        <v>1713580555</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5173,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5192,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711186663</v>
+        <v>1713580584</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5206,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5225,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711265382</v>
+        <v>1713607374</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5239,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5258,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711265424</v>
+        <v>1713607415</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5272,11 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5295,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711269934</v>
+        <v>1713612370</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5309,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5328,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711269973</v>
+        <v>1713612398</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5342,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5361,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711270011</v>
+        <v>1713612412</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5375,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5394,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711349018</v>
+        <v>1713660891</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5408,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5427,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711349064</v>
+        <v>1713660931</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5441,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5460,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711357457</v>
+        <v>1713663736</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5470,15 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5497,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711357498</v>
+        <v>1713665754</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,10 +5507,11 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5530,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711358143</v>
+        <v>1713665780</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5544,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5563,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711358190</v>
+        <v>1713669977</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5573,11 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5596,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711364525</v>
+        <v>1713687604</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5610,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5629,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711364558</v>
+        <v>1713687645</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5393,10 +5639,11 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Quiet</t>
+          <t>LivingRoom.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5662,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711456093</v>
+        <v>1713689900</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5672,15 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5699,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711456125</v>
+        <v>1713692010</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5713,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5732,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711461242</v>
+        <v>1713692046</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5746,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5765,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711461272</v>
+        <v>1713696528</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5779,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5798,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711535059</v>
+        <v>1713767356</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5812,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5831,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711535093</v>
+        <v>1713767390</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5845,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5864,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1711535106</v>
+        <v>1713771960</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5874,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5897,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711545156</v>
+        <v>1713771991</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5907,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>LivingRoom.Noise.state: Noisy</t>
+          <t>LivingRoom.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5930,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711545183</v>
+        <v>1713779454</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5944,1384 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1713779488</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1713784161</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1713784247</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1713784277</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1713789055</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1713854251</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1713854297</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1713854312</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1713862092</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1713862129</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1713870959</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1713870992</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1713876278</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1713876310</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1713957824</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1713957864</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1713966274</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1713966308</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1714036769</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1714036798</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1714042786</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1714042821</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1714042834</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1714135981</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1714136020</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1714141234</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1714141265</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1714179730</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1714179768</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1714180749</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ExcessivelyNoisy</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1714186378</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1714186402</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1714188026</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1714271066</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1714271110</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1714278226</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1714278249</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1714294812</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1714294836</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1714301918</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1714301952</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>LivingRoom.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
